--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-12-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff799768255
+	0x7ff7997682b0
+	0x7ff79954165d
+	0x7ff799599a33
+	0x7ff799599d3c
+	0x7ff7995edf67
+	0x7ff7995eac97
+	0x7ff79958ac29
+	0x7ff79958ba93
+	0x7ff799a7fff0
+	0x7ff799a7a930
+	0x7ff799a99096
+	0x7ff799785754
+	0x7ff79978e6fc
+	0x7ff799771974
+	0x7ff799771b25
+	0x7ff799757852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -641,7 +641,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>£10.15</t>
+          <t>Error: HTTPSConnectionPool(host='diybuildingsupplies.co.uk', port=443): Max retries exceeded with url: /products/celotex-tb4025-high-performance-pir-insulation-2400mm-x-1200mm-x-25mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£11.54</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/30mm-celotex-tb4030-pir-insulation-board-2400mm-x-1200mm-x-30mm</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff704508255
+	0x7ff7045082b0
+	0x7ff7042e165d
+	0x7ff704339a33
+	0x7ff704339d3c
+	0x7ff70438df67
+	0x7ff70438ac97
+	0x7ff70432ac29
+	0x7ff70432ba93
+	0x7ff70481fff0
+	0x7ff70481a930
+	0x7ff704839096
+	0x7ff704525754
+	0x7ff70452e6fc
+	0x7ff704511974
+	0x7ff704511b25
+	0x7ff7044f7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff704508255
+	0x7ff7045082b0
+	0x7ff7042e165d
+	0x7ff704339a33
+	0x7ff704339d3c
+	0x7ff70438df67
+	0x7ff70438ac97
+	0x7ff70432ac29
+	0x7ff70432ba93
+	0x7ff70481fff0
+	0x7ff70481a930
+	0x7ff704839096
+	0x7ff704525754
+	0x7ff70452e6fc
+	0x7ff704511974
+	0x7ff704511b25
+	0x7ff7044f7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff704508255
+	0x7ff7045082b0
+	0x7ff7042e165d
+	0x7ff704339a33
+	0x7ff704339d3c
+	0x7ff70438df67
+	0x7ff70438ac97
+	0x7ff70432ac29
+	0x7ff70432ba93
+	0x7ff70481fff0
+	0x7ff70481a930
+	0x7ff704839096
+	0x7ff704525754
+	0x7ff70452e6fc
+	0x7ff704511974
+	0x7ff704511b25
+	0x7ff7044f7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff704508255
+	0x7ff7045082b0
+	0x7ff7042e165d
+	0x7ff704339a33
+	0x7ff704339d3c
+	0x7ff70438df67
+	0x7ff70438ac97
+	0x7ff70432ac29
+	0x7ff70432ba93
+	0x7ff70481fff0
+	0x7ff70481a930
+	0x7ff704839096
+	0x7ff704525754
+	0x7ff70452e6fc
+	0x7ff704511974
+	0x7ff704511b25
+	0x7ff7044f7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff704508255
+	0x7ff7045082b0
+	0x7ff7042e165d
+	0x7ff704339a33
+	0x7ff704339d3c
+	0x7ff70438df67
+	0x7ff70438ac97
+	0x7ff70432ac29
+	0x7ff70432ba93
+	0x7ff70481fff0
+	0x7ff70481a930
+	0x7ff704839096
+	0x7ff704525754
+	0x7ff70452e6fc
+	0x7ff704511974
+	0x7ff704511b25
+	0x7ff7044f7852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff682948255
+	0x7ff6829482b0
+	0x7ff68272165d
+	0x7ff682779a33
+	0x7ff682779d3c
+	0x7ff6827cdf67
+	0x7ff6827cac97
+	0x7ff68276ac29
+	0x7ff68276ba93
+	0x7ff682c5fff0
+	0x7ff682c5a930
+	0x7ff682c79096
+	0x7ff682965754
+	0x7ff68296e6fc
+	0x7ff682951974
+	0x7ff682951b25
+	0x7ff682937852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff701928255
+	0x7ff7019282b0
+	0x7ff70170165d
+	0x7ff701759a33
+	0x7ff701759d3c
+	0x7ff7017adf67
+	0x7ff7017aac97
+	0x7ff70174ac29
+	0x7ff70174ba93
+	0x7ff701c3fff0
+	0x7ff701c3a930
+	0x7ff701c59096
+	0x7ff701945754
+	0x7ff70194e6fc
+	0x7ff701931974
+	0x7ff701931b25
+	0x7ff701917852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff64e328255
-	0x7ff64e3282b0
-	0x7ff64e10165d
-	0x7ff64e159a33
-	0x7ff64e159d3c
-	0x7ff64e1adf67
-	0x7ff64e1aac97
-	0x7ff64e14ac29
-	0x7ff64e14ba93
-	0x7ff64e63fff0
-	0x7ff64e63a930
-	0x7ff64e659096
-	0x7ff64e345754
-	0x7ff64e34e6fc
-	0x7ff64e331974
-	0x7ff64e331b25
-	0x7ff64e317852
+	0x7ff701928255
+	0x7ff7019282b0
+	0x7ff70170165d
+	0x7ff701759a33
+	0x7ff701759d3c
+	0x7ff7017adf67
+	0x7ff7017aac97
+	0x7ff70174ac29
+	0x7ff70174ba93
+	0x7ff701c3fff0
+	0x7ff701c3a930
+	0x7ff701c59096
+	0x7ff701945754
+	0x7ff70194e6fc
+	0x7ff701931974
+	0x7ff701931b25
+	0x7ff701917852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
